--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487794_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487794_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>M. OKAFOR AUGUSTIN</t>
+          <t>S. FRANCO GARCIA</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>1.6351</v>
+        <v>0.7023</v>
       </c>
       <c r="E2" t="n">
-        <v>2.6839</v>
+        <v>0.678</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.0488</v>
+        <v>0.0243</v>
       </c>
       <c r="G2" t="n">
-        <v>-1.0483</v>
+        <v>-0.2334</v>
       </c>
       <c r="H2" t="n">
-        <v>0.676</v>
+        <v>0.1193</v>
       </c>
       <c r="I2" t="n">
-        <v>-1.7243</v>
+        <v>-0.3527</v>
       </c>
       <c r="J2" t="n">
-        <v>0.3112</v>
+        <v>0.2075</v>
       </c>
       <c r="K2" t="n">
-        <v>0.3985</v>
+        <v>0.1683</v>
       </c>
       <c r="L2" t="n">
-        <v>-0.08740000000000001</v>
+        <v>0.0392</v>
       </c>
       <c r="M2" t="n">
-        <v>-1.3595</v>
+        <v>-0.4409</v>
       </c>
       <c r="N2" t="n">
-        <v>0.2775</v>
+        <v>-0.049</v>
       </c>
       <c r="O2" t="n">
-        <v>-1.6369</v>
+        <v>-0.3919</v>
       </c>
       <c r="P2" t="n">
-        <v>2.2893</v>
+        <v>0.4162</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>2.2893</v>
+        <v>0.4162</v>
       </c>
       <c r="S2" t="n">
-        <v>2.3754</v>
+        <v>0.5195</v>
       </c>
       <c r="T2" t="n">
-        <v>2.3727</v>
+        <v>0.4705</v>
       </c>
       <c r="U2" t="n">
-        <v>0.0026</v>
+        <v>0.0489</v>
       </c>
       <c r="V2" t="n">
-        <v>-1.9813</v>
+        <v>0</v>
       </c>
       <c r="W2" t="n">
         <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>-1.9813</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>S. FRANCO GARCIA</t>
+          <t>M. OKAFOR AUGUSTIN</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.9944</v>
+        <v>0.4182</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9995000000000001</v>
+        <v>1.2909</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.0051</v>
+        <v>-0.8726</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.2334</v>
+        <v>-1.0483</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1193</v>
+        <v>0.676</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.3527</v>
+        <v>-1.7243</v>
       </c>
       <c r="J3" t="n">
-        <v>0.2075</v>
+        <v>0.3112</v>
       </c>
       <c r="K3" t="n">
-        <v>0.1683</v>
+        <v>0.3985</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0392</v>
+        <v>-0.08740000000000001</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.4409</v>
+        <v>-1.3595</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.049</v>
+        <v>0.2775</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.3919</v>
+        <v>-1.6369</v>
       </c>
       <c r="P3" t="n">
-        <v>0.4162</v>
+        <v>2.2893</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>0.4162</v>
+        <v>2.2893</v>
       </c>
       <c r="S3" t="n">
-        <v>0.8116</v>
+        <v>1.1585</v>
       </c>
       <c r="T3" t="n">
-        <v>0.792</v>
+        <v>0.9797</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0196</v>
+        <v>0.1788</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>-1.9813</v>
       </c>
       <c r="W3" t="n">
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>-1.9813</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>J. MENENDEZ GARCIA</t>
+          <t>J. LUIS</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,58 +721,58 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.5585</v>
+        <v>-0.08359999999999999</v>
       </c>
       <c r="E4" t="n">
-        <v>0.09320000000000001</v>
+        <v>0.0598</v>
       </c>
       <c r="F4" t="n">
-        <v>0.4654</v>
+        <v>-0.1433</v>
       </c>
       <c r="G4" t="n">
-        <v>-2.7178</v>
+        <v>-0.7296</v>
       </c>
       <c r="H4" t="n">
-        <v>-2.2264</v>
+        <v>-1.0937</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.4915</v>
+        <v>0.3641</v>
       </c>
       <c r="J4" t="n">
-        <v>0.336</v>
+        <v>0.1359</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.487</v>
+        <v>0.0576</v>
       </c>
       <c r="L4" t="n">
-        <v>0.823</v>
+        <v>0.0784</v>
       </c>
       <c r="M4" t="n">
-        <v>-3.0538</v>
+        <v>-0.8655</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.7394</v>
+        <v>-1.1513</v>
       </c>
       <c r="O4" t="n">
-        <v>-1.3144</v>
+        <v>0.2857</v>
       </c>
       <c r="P4" t="n">
-        <v>0.4162</v>
+        <v>0.6244</v>
       </c>
       <c r="Q4" t="n">
-        <v>-2.0812</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>2.4974</v>
+        <v>0.6244</v>
       </c>
       <c r="S4" t="n">
-        <v>2.8601</v>
+        <v>0.0217</v>
       </c>
       <c r="T4" t="n">
-        <v>1.8384</v>
+        <v>-0.0762</v>
       </c>
       <c r="U4" t="n">
-        <v>1.0218</v>
+        <v>0.0979</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>J. LUIS</t>
+          <t>J. MENENDEZ GARCIA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,58 +799,58 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.3147</v>
+        <v>-0.966</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.1126</v>
+        <v>-1.0203</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.202</v>
+        <v>0.0543</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.7296</v>
+        <v>-2.7178</v>
       </c>
       <c r="H5" t="n">
-        <v>-1.0937</v>
+        <v>-2.2264</v>
       </c>
       <c r="I5" t="n">
-        <v>0.3641</v>
+        <v>-0.4915</v>
       </c>
       <c r="J5" t="n">
-        <v>0.1359</v>
+        <v>0.336</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0576</v>
+        <v>-0.487</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0784</v>
+        <v>0.823</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.8655</v>
+        <v>-3.0538</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.1513</v>
+        <v>-1.7394</v>
       </c>
       <c r="O5" t="n">
-        <v>0.2857</v>
+        <v>-1.3144</v>
       </c>
       <c r="P5" t="n">
-        <v>0.6244</v>
+        <v>0.4162</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-2.0812</v>
       </c>
       <c r="R5" t="n">
-        <v>0.6244</v>
+        <v>2.4974</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.2094</v>
+        <v>1.3356</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.2486</v>
+        <v>0.7249</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0391</v>
+        <v>0.6107</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -877,10 +877,10 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.5638</v>
+        <v>-1.2423</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.7748</v>
+        <v>-1.4534</v>
       </c>
       <c r="F6" t="n">
         <v>0.2111</v>
@@ -922,10 +922,10 @@
         <v>1.0406</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>0.3215</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.4319</v>
+        <v>-0.1105</v>
       </c>
       <c r="U6" t="n">
         <v>0.4319</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-2.0808</v>
+        <v>-1.333</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.5621</v>
+        <v>0.0389</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.5187</v>
+        <v>-1.3719</v>
       </c>
       <c r="G7" t="n">
         <v>-2.3181</v>
@@ -1000,13 +1000,13 @@
         <v>3.1218</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.3464</v>
+        <v>0.4014</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.6186</v>
+        <v>-0.0175</v>
       </c>
       <c r="U7" t="n">
-        <v>0.2721</v>
+        <v>0.4189</v>
       </c>
       <c r="V7" t="n">
         <v>0.5838</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.2424</v>
+        <v>-2.2336</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.017</v>
+        <v>0.1973</v>
       </c>
       <c r="F8" t="n">
-        <v>-2.2254</v>
+        <v>-2.4309</v>
       </c>
       <c r="G8" t="n">
         <v>-2.9597</v>
@@ -1078,13 +1078,13 @@
         <v>2.0812</v>
       </c>
       <c r="S8" t="n">
-        <v>0.4873</v>
+        <v>0.4961</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.1743</v>
+        <v>0.0401</v>
       </c>
       <c r="U8" t="n">
-        <v>0.6616</v>
+        <v>0.4561</v>
       </c>
       <c r="V8" t="n">
         <v>0.23</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.0324</v>
+        <v>-2.5591</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.1638</v>
+        <v>-1.4557</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.8686</v>
+        <v>-1.1035</v>
       </c>
       <c r="G9" t="n">
         <v>-2.5994</v>
@@ -1156,13 +1156,13 @@
         <v>3.3299</v>
       </c>
       <c r="S9" t="n">
-        <v>0.4025</v>
+        <v>0.8758</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.1619</v>
+        <v>0.5463</v>
       </c>
       <c r="U9" t="n">
-        <v>0.5644</v>
+        <v>0.3295</v>
       </c>
       <c r="V9" t="n">
         <v>-1.0437</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>D. RAMÍREZ SÁNCHEZ</t>
+          <t>J. REILLY</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,64 +1189,64 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.1755</v>
+        <v>-2.5929</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.9841</v>
+        <v>-1.3363</v>
       </c>
       <c r="F10" t="n">
-        <v>0.8086</v>
+        <v>-1.2566</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.8601</v>
+        <v>-2.5267</v>
       </c>
       <c r="H10" t="n">
-        <v>0.3498</v>
+        <v>0.2002</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.2099</v>
+        <v>-2.7269</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.9866</v>
+        <v>1.1149</v>
       </c>
       <c r="K10" t="n">
-        <v>0.403</v>
+        <v>1.172</v>
       </c>
       <c r="L10" t="n">
-        <v>-1.3896</v>
+        <v>-0.0572</v>
       </c>
       <c r="M10" t="n">
-        <v>0.1265</v>
+        <v>-3.6415</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.0532</v>
+        <v>-0.9719</v>
       </c>
       <c r="O10" t="n">
-        <v>0.1796</v>
+        <v>-2.6697</v>
       </c>
       <c r="P10" t="n">
-        <v>-2.4974</v>
+        <v>0.6244</v>
       </c>
       <c r="Q10" t="n">
-        <v>-3.1218</v>
+        <v>-2.0812</v>
       </c>
       <c r="R10" t="n">
-        <v>0.6244</v>
+        <v>2.7055</v>
       </c>
       <c r="S10" t="n">
-        <v>0.182</v>
+        <v>-0.4606</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.1057</v>
+        <v>-0.37</v>
       </c>
       <c r="U10" t="n">
-        <v>0.2877</v>
+        <v>-0.0906</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>-0.23</v>
       </c>
       <c r="W10" t="n">
-        <v>0.23</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
         <v>-0.23</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>J. REILLY</t>
+          <t>D. RAMÍREZ SÁNCHEZ</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,64 +1267,64 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.8971</v>
+        <v>-2.9025</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.2588</v>
+        <v>-3.7698</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.6383</v>
+        <v>0.8673</v>
       </c>
       <c r="G11" t="n">
-        <v>-2.5267</v>
+        <v>-0.8601</v>
       </c>
       <c r="H11" t="n">
-        <v>0.2002</v>
+        <v>0.3498</v>
       </c>
       <c r="I11" t="n">
-        <v>-2.7269</v>
+        <v>-1.2099</v>
       </c>
       <c r="J11" t="n">
-        <v>1.1149</v>
+        <v>-0.9866</v>
       </c>
       <c r="K11" t="n">
-        <v>1.172</v>
+        <v>0.403</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.0572</v>
+        <v>-1.3896</v>
       </c>
       <c r="M11" t="n">
-        <v>-3.6415</v>
+        <v>0.1265</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.9719</v>
+        <v>-0.0532</v>
       </c>
       <c r="O11" t="n">
-        <v>-2.6697</v>
+        <v>0.1796</v>
       </c>
       <c r="P11" t="n">
+        <v>-2.4974</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>-3.1218</v>
+      </c>
+      <c r="R11" t="n">
         <v>0.6244</v>
       </c>
-      <c r="Q11" t="n">
-        <v>-2.0812</v>
-      </c>
-      <c r="R11" t="n">
-        <v>2.7055</v>
-      </c>
       <c r="S11" t="n">
-        <v>-1.7648</v>
+        <v>0.4551</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.2925</v>
+        <v>0.1086</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.4723</v>
+        <v>0.3464</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.23</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>0.23</v>
       </c>
       <c r="X11" t="n">
         <v>-0.23</v>
@@ -1345,10 +1345,10 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-13.1187</v>
+        <v>-12.7925</v>
       </c>
       <c r="E12" t="n">
-        <v>-7.0966</v>
+        <v>-6.7706</v>
       </c>
       <c r="F12" t="n">
         <v>-6.0218</v>
@@ -1390,10 +1390,10 @@
         <v>18.7307</v>
       </c>
       <c r="S12" t="n">
-        <v>4.7983</v>
+        <v>5.1246</v>
       </c>
       <c r="T12" t="n">
-        <v>1.9696</v>
+        <v>2.2959</v>
       </c>
       <c r="U12" t="n">
         <v>2.8285</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>10.2261</v>
+        <v>10.9864</v>
       </c>
       <c r="E13" t="n">
-        <v>8.770099999999999</v>
+        <v>8.984400000000001</v>
       </c>
       <c r="F13" t="n">
-        <v>1.456</v>
+        <v>2.0021</v>
       </c>
       <c r="G13" t="n">
         <v>7.1638</v>
@@ -1468,13 +1468,13 @@
         <v>2.0812</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.4809</v>
+        <v>-0.7206</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.1091</v>
+        <v>-0.8948</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.3718</v>
+        <v>0.1743</v>
       </c>
       <c r="V13" t="n">
         <v>3.5026</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>6.754</v>
+        <v>6.9541</v>
       </c>
       <c r="E14" t="n">
-        <v>4.2775</v>
+        <v>4.1703</v>
       </c>
       <c r="F14" t="n">
-        <v>2.4766</v>
+        <v>2.7838</v>
       </c>
       <c r="G14" t="n">
         <v>3.5449</v>
@@ -1546,13 +1546,13 @@
         <v>2.7055</v>
       </c>
       <c r="S14" t="n">
-        <v>0.0229</v>
+        <v>0.223</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.2519</v>
+        <v>-0.359</v>
       </c>
       <c r="U14" t="n">
-        <v>0.2748</v>
+        <v>0.582</v>
       </c>
       <c r="V14" t="n">
         <v>1.5213</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.5106</v>
+        <v>3.3868</v>
       </c>
       <c r="E15" t="n">
-        <v>2.1625</v>
+        <v>1.8411</v>
       </c>
       <c r="F15" t="n">
-        <v>1.3481</v>
+        <v>1.5457</v>
       </c>
       <c r="G15" t="n">
         <v>2.5535</v>
@@ -1624,13 +1624,13 @@
         <v>1.0406</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.0835</v>
+        <v>-0.2073</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.0033</v>
+        <v>-0.3248</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.08019999999999999</v>
+        <v>0.1175</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>I. ORDOÑEZ OCHOA</t>
+          <t>I. HANEY</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,64 +1657,64 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.0071</v>
+        <v>1.5548</v>
       </c>
       <c r="E16" t="n">
-        <v>0.4539</v>
+        <v>-0.7694</v>
       </c>
       <c r="F16" t="n">
-        <v>1.5533</v>
+        <v>2.3242</v>
       </c>
       <c r="G16" t="n">
-        <v>2.466</v>
+        <v>1.8723</v>
       </c>
       <c r="H16" t="n">
-        <v>0.949</v>
+        <v>3.5223</v>
       </c>
       <c r="I16" t="n">
-        <v>1.5169</v>
+        <v>-1.65</v>
       </c>
       <c r="J16" t="n">
-        <v>3.495</v>
+        <v>2.6524</v>
       </c>
       <c r="K16" t="n">
-        <v>1.1617</v>
+        <v>4.0207</v>
       </c>
       <c r="L16" t="n">
-        <v>2.3333</v>
+        <v>-1.3683</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.029</v>
+        <v>-0.78</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.2126</v>
+        <v>-0.4984</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.8164</v>
+        <v>-0.2817</v>
       </c>
       <c r="P16" t="n">
-        <v>-2.9137</v>
+        <v>-0.2081</v>
       </c>
       <c r="Q16" t="n">
-        <v>-5.2029</v>
+        <v>-3.1218</v>
       </c>
       <c r="R16" t="n">
-        <v>2.2893</v>
+        <v>2.9137</v>
       </c>
       <c r="S16" t="n">
-        <v>0.9512</v>
+        <v>-0.1094</v>
       </c>
       <c r="T16" t="n">
-        <v>0.6582</v>
+        <v>-0.3</v>
       </c>
       <c r="U16" t="n">
-        <v>0.293</v>
+        <v>0.1906</v>
       </c>
       <c r="V16" t="n">
-        <v>1.5036</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>1.5036</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
         <v>0</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>I. HANEY</t>
+          <t>I. ORDOÑEZ OCHOA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,64 +1735,64 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.6452</v>
+        <v>1.2238</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.3052</v>
+        <v>-0.2962</v>
       </c>
       <c r="F17" t="n">
-        <v>1.9504</v>
+        <v>1.52</v>
       </c>
       <c r="G17" t="n">
-        <v>1.8723</v>
+        <v>2.466</v>
       </c>
       <c r="H17" t="n">
-        <v>3.5223</v>
+        <v>0.949</v>
       </c>
       <c r="I17" t="n">
-        <v>-1.65</v>
+        <v>1.5169</v>
       </c>
       <c r="J17" t="n">
-        <v>2.6524</v>
+        <v>3.495</v>
       </c>
       <c r="K17" t="n">
-        <v>4.0207</v>
+        <v>1.1617</v>
       </c>
       <c r="L17" t="n">
-        <v>-1.3683</v>
+        <v>2.3333</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.78</v>
+        <v>-1.029</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.4984</v>
+        <v>-0.2126</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.2817</v>
+        <v>-0.8164</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.2081</v>
+        <v>-2.9137</v>
       </c>
       <c r="Q17" t="n">
-        <v>-3.1218</v>
+        <v>-5.2029</v>
       </c>
       <c r="R17" t="n">
-        <v>2.9137</v>
+        <v>2.2893</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.019</v>
+        <v>0.1679</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.8358</v>
+        <v>-0.0919</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.1833</v>
+        <v>0.2597</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>1.5036</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.5036</v>
       </c>
       <c r="X17" t="n">
         <v>0</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.4832</v>
+        <v>0.6768999999999999</v>
       </c>
       <c r="E18" t="n">
         <v>-1.8175</v>
       </c>
       <c r="F18" t="n">
-        <v>2.3007</v>
+        <v>2.4945</v>
       </c>
       <c r="G18" t="n">
         <v>0.5154</v>
@@ -1858,13 +1858,13 @@
         <v>2.2893</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.0104</v>
+        <v>0.1833</v>
       </c>
       <c r="T18" t="n">
         <v>-0.1214</v>
       </c>
       <c r="U18" t="n">
-        <v>0.111</v>
+        <v>0.3047</v>
       </c>
       <c r="V18" t="n">
         <v>-0.23</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.561</v>
+        <v>-0.8427</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.4899</v>
+        <v>-1.0613</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.0712</v>
+        <v>0.2185</v>
       </c>
       <c r="G19" t="n">
         <v>0.1765</v>
@@ -1936,13 +1936,13 @@
         <v>1.6649</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.9675</v>
+        <v>-0.2492</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.64</v>
+        <v>-0.2114</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.3275</v>
+        <v>-0.0378</v>
       </c>
       <c r="V19" t="n">
         <v>-0.3538</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.7679</v>
+        <v>-2.5203</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.3374</v>
+        <v>-1.5518</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.4305</v>
+        <v>-0.9686</v>
       </c>
       <c r="G21" t="n">
         <v>0.4938</v>
@@ -2092,13 +2092,13 @@
         <v>0.6244</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.6374</v>
+        <v>-0.3898</v>
       </c>
       <c r="T21" t="n">
-        <v>0.0619</v>
+        <v>-0.1524</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.6993</v>
+        <v>-0.2374</v>
       </c>
       <c r="V21" t="n">
         <v>-1.1675</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.362</v>
+        <v>-3.6271</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.6268</v>
+        <v>-3.4125</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.7353</v>
+        <v>-0.2146</v>
       </c>
       <c r="G22" t="n">
         <v>-2.0988</v>
@@ -2170,13 +2170,13 @@
         <v>1.0406</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.2226</v>
+        <v>-0.4877</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.5219</v>
+        <v>-0.3076</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.7007</v>
+        <v>-0.18</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2203,37 +2203,37 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>13.1188</v>
+        <v>15.9762</v>
       </c>
       <c r="E23" t="n">
-        <v>6.022</v>
+        <v>6.021900000000002</v>
       </c>
       <c r="F23" t="n">
-        <v>7.096799999999999</v>
+        <v>9.954299999999998</v>
       </c>
       <c r="G23" t="n">
         <v>16.3894</v>
       </c>
       <c r="H23" t="n">
-        <v>4.980000000000001</v>
+        <v>4.98</v>
       </c>
       <c r="I23" t="n">
         <v>11.4095</v>
       </c>
       <c r="J23" t="n">
-        <v>19.77980000000001</v>
+        <v>19.7798</v>
       </c>
       <c r="K23" t="n">
-        <v>5.370199999999999</v>
+        <v>5.370200000000001</v>
       </c>
       <c r="L23" t="n">
         <v>14.4098</v>
       </c>
       <c r="M23" t="n">
-        <v>-3.3904</v>
+        <v>-3.390400000000001</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.3900000000000001</v>
+        <v>-0.3900000000000002</v>
       </c>
       <c r="O23" t="n">
         <v>-3.0003</v>
@@ -2248,16 +2248,16 @@
         <v>16.6495</v>
       </c>
       <c r="S23" t="n">
-        <v>-4.7982</v>
+        <v>-1.9408</v>
       </c>
       <c r="T23" t="n">
         <v>-2.8285</v>
       </c>
       <c r="U23" t="n">
-        <v>-1.9697</v>
+        <v>0.8878999999999999</v>
       </c>
       <c r="V23" t="n">
-        <v>3.608699999999999</v>
+        <v>3.6087</v>
       </c>
       <c r="W23" t="n">
         <v>7.801200000000001</v>
